--- a/mystkdatav2/dividend_database.xlsx
+++ b/mystkdatav2/dividend_database.xlsx
@@ -8,6 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配息記錄" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年度統計" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="月度統計" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="股票統計" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="進階統計" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,36 +487,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2023-07</t>
+          <t>2023-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>台新金</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17777</v>
+        <v>11800</v>
       </c>
       <c r="E2" t="n">
-        <v>1.267371</v>
+        <v>1.4</v>
       </c>
       <c r="F2" t="n">
-        <v>22530.054267</v>
+        <v>16520</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2023-07-26</t>
+          <t>2023-06-01</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-07-18 16:12:37</t>
+          <t>2025-07-18 18:08:47</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -529,36 +533,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2023-08</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2892</t>
-        </is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2887</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>台新金</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15602</v>
+        <v>17777</v>
       </c>
       <c r="E3" t="n">
-        <v>1.628641</v>
+        <v>1.267371</v>
       </c>
       <c r="F3" t="n">
-        <v>25410.056882</v>
+        <v>22530.054267</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2023-08-11</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-07-18 16:12:40</t>
+          <t>2025-07-18 17:36:38</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -575,36 +577,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2023-08</t>
+          <t>2023-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>台新金</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5500</v>
+        <v>17777</v>
       </c>
       <c r="E4" t="n">
-        <v>10.35294</v>
+        <v>1.267371</v>
       </c>
       <c r="F4" t="n">
-        <v>56941.17</v>
+        <v>22530.054267</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-07-26</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-07-18 16:12:39</t>
+          <t>2025-07-18 18:08:59</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -621,36 +623,34 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2024-02</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>00878</t>
-        </is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2892</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>44000</v>
+        <v>15602</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4</v>
+        <v>1.628641</v>
       </c>
       <c r="F5" t="n">
-        <v>17600</v>
+        <v>25410.056882</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:20</t>
+          <t>2025-07-18 17:36:41</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -667,41 +667,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>00687B</t>
-        </is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5871</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">國泰20年美債         </t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5000</v>
+        <v>5500</v>
       </c>
       <c r="E6" t="n">
-        <v>0.34</v>
+        <v>10.35294</v>
       </c>
       <c r="F6" t="n">
-        <v>1700</v>
+        <v>56941.17</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:00</t>
+          <t>2025-07-18 17:36:40</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -713,36 +711,36 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7000</v>
+        <v>15602</v>
       </c>
       <c r="E7" t="n">
-        <v>0.88</v>
+        <v>1.628641</v>
       </c>
       <c r="F7" t="n">
-        <v>6160</v>
+        <v>25410.056882</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2023-08-11</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:21</t>
+          <t>2025-07-18 18:09:02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -759,41 +757,41 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2023-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>00751B</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">元大AAA至A公司債      </t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>52000</v>
+        <v>5500</v>
       </c>
       <c r="E8" t="n">
-        <v>0.44</v>
+        <v>10.35294</v>
       </c>
       <c r="F8" t="n">
-        <v>22880</v>
+        <v>56941.17</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2023-08-01</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:00</t>
+          <t>2025-07-18 18:09:00</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -805,41 +803,41 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2024-03</t>
+          <t>2024-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>00937B</t>
+          <t>00878</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">群益ESG投等債20+     </t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>145000</v>
+        <v>44000</v>
       </c>
       <c r="E9" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="F9" t="n">
-        <v>12180</v>
+        <v>17600</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2024-03-18</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2025-07-18 16:12:59</t>
+          <t>2025-07-18 18:09:45</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -851,41 +849,41 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>00687B</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t xml:space="preserve">國泰20年美債         </t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13300</v>
+        <v>5000</v>
       </c>
       <c r="E10" t="n">
-        <v>0.79</v>
+        <v>0.34</v>
       </c>
       <c r="F10" t="n">
-        <v>10507</v>
+        <v>1700</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:18</t>
+          <t>2025-07-18 18:09:24</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -897,41 +895,41 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2024-04</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>00937B</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">群益ESG投等債20+     </t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>145000</v>
+        <v>7000</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="F11" t="n">
-        <v>12180</v>
+        <v>6160</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2024-04-18</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2025-07-18 16:12:59</t>
+          <t>2025-07-18 18:09:46</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -943,41 +941,41 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>00878</t>
+          <t>00751B</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t xml:space="preserve">元大AAA至A公司債      </t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>45000</v>
+        <v>52000</v>
       </c>
       <c r="E12" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
       </c>
       <c r="F12" t="n">
-        <v>22950</v>
+        <v>22880</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:20</t>
+          <t>2025-07-18 18:09:25</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -989,7 +987,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2024-05</t>
+          <t>2024-03</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1013,12 +1011,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2024-05-17</t>
+          <t>2024-03-18</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2025-07-18 16:12:59</t>
+          <t>2025-07-18 18:09:23</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1035,41 +1033,41 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>00687B</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">國泰20年美債         </t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5000</v>
+        <v>13300</v>
       </c>
       <c r="E14" t="n">
-        <v>0.34</v>
+        <v>0.79</v>
       </c>
       <c r="F14" t="n">
-        <v>1700</v>
+        <v>10507</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:00</t>
+          <t>2025-07-18 18:09:42</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1081,41 +1079,41 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00937B</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t xml:space="preserve">群益ESG投等債20+     </t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8571</v>
+        <v>145000</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>12856.5</v>
+        <v>12180</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-04-18</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:21</t>
+          <t>2025-07-18 18:09:23</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1127,41 +1125,41 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>00751B</t>
+          <t>00878</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">元大AAA至A公司債      </t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>52000</v>
+        <v>45000</v>
       </c>
       <c r="E16" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="F16" t="n">
-        <v>24440</v>
+        <v>22950</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:00</t>
+          <t>2025-07-18 18:09:45</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1173,36 +1171,36 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2024-06</t>
+          <t>2024-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>00857B</t>
+          <t>00937B</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">永豐20年美公債        </t>
+          <t xml:space="preserve">群益ESG投等債20+     </t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2000</v>
+        <v>145000</v>
       </c>
       <c r="E17" t="n">
-        <v>0.21</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>420</v>
+        <v>12180</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-05-17</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:02</t>
+          <t>2025-07-18 18:09:23</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1224,31 +1222,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>00937B</t>
+          <t>00687B</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">群益ESG投等債20+     </t>
+          <t xml:space="preserve">國泰20年美債         </t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>145000</v>
+        <v>5000</v>
       </c>
       <c r="E18" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="F18" t="n">
-        <v>12180</v>
+        <v>1700</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2025-07-18 16:12:59</t>
+          <t>2025-07-18 18:09:24</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1265,36 +1263,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13630</v>
+        <v>8571</v>
       </c>
       <c r="E19" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="F19" t="n">
-        <v>14584.1</v>
+        <v>12856.5</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:18</t>
+          <t>2025-07-18 18:09:46</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1311,41 +1309,41 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>00934</t>
+          <t>00751B</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>中信成長高股息</t>
+          <t xml:space="preserve">元大AAA至A公司債      </t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>3000</v>
+        <v>52000</v>
       </c>
       <c r="E20" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="F20" t="n">
-        <v>990</v>
+        <v>24440</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:37</t>
+          <t>2025-07-18 18:09:25</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1357,36 +1355,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>00937B</t>
+          <t>00857B</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">群益ESG投等債20+     </t>
+          <t xml:space="preserve">永豐20年美公債        </t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>145000</v>
+        <v>2000</v>
       </c>
       <c r="E21" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="F21" t="n">
-        <v>12180</v>
+        <v>420</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2024-07-19</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2025-07-18 16:12:59</t>
+          <t>2025-07-18 18:09:27</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1403,41 +1401,41 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>00937B</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>台中銀</t>
+          <t xml:space="preserve">群益ESG投等債20+     </t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11000</v>
+        <v>145000</v>
       </c>
       <c r="E22" t="n">
-        <v>1.415531</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>15570.841</v>
+        <v>12180</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:40</t>
+          <t>2025-07-18 18:09:23</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1449,36 +1447,36 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2024-07</t>
+          <t>2024-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>全台</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>4000</v>
+        <v>11800</v>
       </c>
       <c r="E23" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="F23" t="n">
-        <v>6400</v>
+        <v>23600</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2024-07-02</t>
+          <t>2024-06-05</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:32</t>
+          <t>2025-07-18 18:09:51</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1500,31 +1498,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>9900</v>
+        <v>13630</v>
       </c>
       <c r="E24" t="n">
-        <v>9.549018999999999</v>
+        <v>1.07</v>
       </c>
       <c r="F24" t="n">
-        <v>94535.28809999999</v>
+        <v>14584.1</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:39</t>
+          <t>2025-07-18 18:09:42</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1541,36 +1539,36 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>00878</t>
+          <t>00934</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>中信成長高股息</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>47448</v>
+        <v>3000</v>
       </c>
       <c r="E25" t="n">
-        <v>0.55</v>
+        <v>0.33</v>
       </c>
       <c r="F25" t="n">
-        <v>26096.4</v>
+        <v>990</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:20</t>
+          <t>2025-07-18 18:10:01</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1587,41 +1585,41 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>00934</t>
+          <t>00937B</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>中信成長高股息</t>
+          <t xml:space="preserve">群益ESG投等債20+     </t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13541</v>
+        <v>145000</v>
       </c>
       <c r="E26" t="n">
-        <v>0.14</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>1895.74</v>
+        <v>12180</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:37</t>
+          <t>2025-07-18 18:09:23</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1633,41 +1631,41 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>00937B</t>
+          <t>2812</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">群益ESG投等債20+     </t>
+          <t>台中銀</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>145000</v>
+        <v>11000</v>
       </c>
       <c r="E27" t="n">
-        <v>0.082</v>
+        <v>1.415531</v>
       </c>
       <c r="F27" t="n">
-        <v>11890</v>
+        <v>15570.841</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2025-07-18 16:12:59</t>
+          <t>2025-07-18 18:10:05</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1679,41 +1677,41 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>00948B</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">中信優息投資級債        </t>
+          <t>全台</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>160000</v>
+        <v>4000</v>
       </c>
       <c r="E28" t="n">
-        <v>0.055</v>
+        <v>1.6</v>
       </c>
       <c r="F28" t="n">
-        <v>8800</v>
+        <v>6400</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2024-08-16</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:15</t>
+          <t>2025-07-18 18:09:56</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1725,36 +1723,36 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2024-08</t>
+          <t>2024-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>台新金</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>17777</v>
+        <v>9900</v>
       </c>
       <c r="E29" t="n">
-        <v>1.3</v>
+        <v>9.549018999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>23110.1</v>
+        <v>94535.28809999999</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2024-08-06</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:44</t>
+          <t>2025-07-18 18:10:04</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1776,31 +1774,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>00878</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15602</v>
+        <v>47448</v>
       </c>
       <c r="E30" t="n">
-        <v>1.648058</v>
+        <v>0.55</v>
       </c>
       <c r="F30" t="n">
-        <v>25713.000916</v>
+        <v>26096.4</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:44</t>
+          <t>2025-07-18 18:09:45</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1822,31 +1820,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>00934</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>茂順</t>
+          <t>中信成長高股息</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1000</v>
+        <v>13541</v>
       </c>
       <c r="E31" t="n">
-        <v>7</v>
+        <v>0.14</v>
       </c>
       <c r="F31" t="n">
-        <v>7000</v>
+        <v>1895.74</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:44</t>
+          <t>2025-07-18 18:10:01</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1863,36 +1861,36 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>00687B</t>
+          <t>00937B</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">國泰20年美債         </t>
+          <t xml:space="preserve">群益ESG投等債20+     </t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5000</v>
+        <v>145000</v>
       </c>
       <c r="E32" t="n">
-        <v>0.42</v>
+        <v>0.082</v>
       </c>
       <c r="F32" t="n">
-        <v>2100</v>
+        <v>11890</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:00</t>
+          <t>2025-07-18 18:09:23</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1909,41 +1907,41 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00948B</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t xml:space="preserve">中信優息投資級債        </t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12829</v>
+        <v>160000</v>
       </c>
       <c r="E33" t="n">
-        <v>1.5</v>
+        <v>0.055</v>
       </c>
       <c r="F33" t="n">
-        <v>19243.5</v>
+        <v>8800</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-16</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:21</t>
+          <t>2025-07-18 18:09:39</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -1955,41 +1953,41 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>00751B</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">元大AAA至A公司債      </t>
+          <t>台新金</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>52000</v>
+        <v>17777</v>
       </c>
       <c r="E34" t="n">
-        <v>0.46</v>
+        <v>1.3</v>
       </c>
       <c r="F34" t="n">
-        <v>23920</v>
+        <v>23110.1</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-06</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:00</t>
+          <t>2025-07-18 18:10:09</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2001,41 +1999,41 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>00857B</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">永豐20年美公債        </t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>17000</v>
+        <v>15602</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3</v>
+        <v>1.648058</v>
       </c>
       <c r="F35" t="n">
-        <v>5100</v>
+        <v>25713.000916</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:02</t>
+          <t>2025-07-18 18:10:09</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2047,36 +2045,36 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2024-09</t>
+          <t>2024-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>00934</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>中信成長高股息</t>
+          <t>茂順</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>21081</v>
+        <v>1000</v>
       </c>
       <c r="E36" t="n">
-        <v>0.142</v>
+        <v>7</v>
       </c>
       <c r="F36" t="n">
-        <v>2993.502</v>
+        <v>7000</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2024-09-18</t>
+          <t>2024-08-08</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:37</t>
+          <t>2025-07-18 18:10:09</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2098,31 +2096,31 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>00937B</t>
+          <t>00687B</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">群益ESG投等債20+     </t>
+          <t xml:space="preserve">國泰20年美債         </t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>145000</v>
+        <v>5000</v>
       </c>
       <c r="E37" t="n">
-        <v>0.082</v>
+        <v>0.42</v>
       </c>
       <c r="F37" t="n">
-        <v>11890</v>
+        <v>2100</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2024-09-23</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2025-07-18 16:12:59</t>
+          <t>2025-07-18 18:09:24</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2144,22 +2142,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>00948B</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">中信優息投資級債        </t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>160000</v>
+        <v>12829</v>
       </c>
       <c r="E38" t="n">
-        <v>0.053</v>
+        <v>1.5</v>
       </c>
       <c r="F38" t="n">
-        <v>8480</v>
+        <v>19243.5</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2168,12 +2166,12 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:15</t>
+          <t>2025-07-18 18:09:46</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2190,36 +2188,36 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>00751B</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>中租-KY</t>
+          <t xml:space="preserve">元大AAA至A公司債      </t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>9900</v>
+        <v>52000</v>
       </c>
       <c r="E39" t="n">
-        <v>0.305275</v>
+        <v>0.46</v>
       </c>
       <c r="F39" t="n">
-        <v>3022.2225</v>
+        <v>23920</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2024-09-05</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:39</t>
+          <t>2025-07-18 18:09:25</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2231,41 +2229,41 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>00857B</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t xml:space="preserve">永豐20年美公債        </t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>15790</v>
+        <v>17000</v>
       </c>
       <c r="E40" t="n">
-        <v>1.07</v>
+        <v>0.3</v>
       </c>
       <c r="F40" t="n">
-        <v>16895.3</v>
+        <v>5100</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:18</t>
+          <t>2025-07-18 18:09:27</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2277,7 +2275,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2291,22 +2289,22 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>26631</v>
+        <v>21081</v>
       </c>
       <c r="E41" t="n">
-        <v>0.139</v>
+        <v>0.142</v>
       </c>
       <c r="F41" t="n">
-        <v>3701.709</v>
+        <v>2993.502</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:37</t>
+          <t>2025-07-18 18:10:01</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2323,7 +2321,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2347,12 +2345,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2024-10-22</t>
+          <t>2024-09-23</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2025-07-18 16:12:59</t>
+          <t>2025-07-18 18:09:23</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2369,7 +2367,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2393,12 +2391,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-09-18</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:15</t>
+          <t>2025-07-18 18:09:39</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2415,36 +2413,36 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>00878</t>
+          <t>5871</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>中租-KY</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>50188</v>
+        <v>9900</v>
       </c>
       <c r="E44" t="n">
-        <v>0.55</v>
+        <v>0.305275</v>
       </c>
       <c r="F44" t="n">
-        <v>27603.4</v>
+        <v>3022.2225</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-09-05</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:20</t>
+          <t>2025-07-18 18:10:04</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2461,36 +2459,36 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>00934</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>中信成長高股息</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>32226</v>
+        <v>15790</v>
       </c>
       <c r="E45" t="n">
-        <v>0.115</v>
+        <v>1.07</v>
       </c>
       <c r="F45" t="n">
-        <v>3705.99</v>
+        <v>16895.3</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:37</t>
+          <t>2025-07-18 18:09:43</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2507,41 +2505,41 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>00937B</t>
+          <t>00934</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">群益ESG投等債20+     </t>
+          <t>中信成長高股息</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>145000</v>
+        <v>26631</v>
       </c>
       <c r="E46" t="n">
-        <v>0.082</v>
+        <v>0.139</v>
       </c>
       <c r="F46" t="n">
-        <v>11890</v>
+        <v>3701.709</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2025-07-18 16:12:59</t>
+          <t>2025-07-18 18:10:01</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -2553,36 +2551,36 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>00948B</t>
+          <t>00937B</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">中信優息投資級債        </t>
+          <t xml:space="preserve">群益ESG投等債20+     </t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>160000</v>
+        <v>145000</v>
       </c>
       <c r="E47" t="n">
-        <v>0.052</v>
+        <v>0.082</v>
       </c>
       <c r="F47" t="n">
-        <v>8320</v>
+        <v>11890</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-10-22</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:15</t>
+          <t>2025-07-18 18:09:23</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2599,36 +2597,36 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>00687B</t>
+          <t>00948B</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">國泰20年美債         </t>
+          <t xml:space="preserve">中信優息投資級債        </t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5000</v>
+        <v>160000</v>
       </c>
       <c r="E48" t="n">
-        <v>0.38</v>
+        <v>0.053</v>
       </c>
       <c r="F48" t="n">
-        <v>1900</v>
+        <v>8480</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:00</t>
+          <t>2025-07-18 18:09:39</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2645,36 +2643,36 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00878</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>15305</v>
+        <v>50188</v>
       </c>
       <c r="E49" t="n">
-        <v>1.4</v>
+        <v>0.55</v>
       </c>
       <c r="F49" t="n">
-        <v>21427</v>
+        <v>27603.4</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:21</t>
+          <t>2025-07-18 18:09:45</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2691,41 +2689,41 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>00751B</t>
+          <t>00934</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">元大AAA至A公司債      </t>
+          <t>中信成長高股息</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>52000</v>
+        <v>32226</v>
       </c>
       <c r="E50" t="n">
-        <v>0.46</v>
+        <v>0.115</v>
       </c>
       <c r="F50" t="n">
-        <v>23920</v>
+        <v>3705.99</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:00</t>
+          <t>2025-07-18 18:10:01</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -2737,36 +2735,36 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>00857B</t>
+          <t>00937B</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">永豐20年美公債        </t>
+          <t xml:space="preserve">群益ESG投等債20+     </t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>52000</v>
+        <v>145000</v>
       </c>
       <c r="E51" t="n">
-        <v>0.31</v>
+        <v>0.082</v>
       </c>
       <c r="F51" t="n">
-        <v>16120</v>
+        <v>11890</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>2024-11-21</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:02</t>
+          <t>2025-07-18 18:09:23</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2783,41 +2781,41 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2024-11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>00934</t>
+          <t>00948B</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>中信成長高股息</t>
+          <t xml:space="preserve">中信優息投資級債        </t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>34859</v>
+        <v>160000</v>
       </c>
       <c r="E52" t="n">
-        <v>0.023</v>
+        <v>0.052</v>
       </c>
       <c r="F52" t="n">
-        <v>801.7569999999999</v>
+        <v>8320</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2024-12-17</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:37</t>
+          <t>2025-07-18 18:09:39</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -2834,31 +2832,31 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>00937B</t>
+          <t>00687B</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">群益ESG投等債20+     </t>
+          <t xml:space="preserve">國泰20年美債         </t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>145000</v>
+        <v>5000</v>
       </c>
       <c r="E53" t="n">
-        <v>0.082</v>
+        <v>0.38</v>
       </c>
       <c r="F53" t="n">
-        <v>11890</v>
+        <v>1900</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2024-12-20</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2025-07-18 16:12:59</t>
+          <t>2025-07-18 18:09:24</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2880,22 +2878,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>00948B</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">中信優息投資級債        </t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>160000</v>
+        <v>15305</v>
       </c>
       <c r="E54" t="n">
-        <v>0.052</v>
+        <v>1.4</v>
       </c>
       <c r="F54" t="n">
-        <v>8320</v>
+        <v>21427</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2904,12 +2902,12 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:15</t>
+          <t>2025-07-18 18:09:46</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -2921,41 +2919,41 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>00751B</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t xml:space="preserve">元大AAA至A公司債      </t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>16636</v>
+        <v>52000</v>
       </c>
       <c r="E55" t="n">
-        <v>1.07</v>
+        <v>0.46</v>
       </c>
       <c r="F55" t="n">
-        <v>17800.52</v>
+        <v>23920</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:16</t>
+          <t>2025-07-18 18:09:25</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -2967,41 +2965,41 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>00934</t>
+          <t>00857B</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>中信成長高股息</t>
+          <t xml:space="preserve">永豐20年美公債        </t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>37493</v>
+        <v>52000</v>
       </c>
       <c r="E56" t="n">
-        <v>0.026</v>
+        <v>0.31</v>
       </c>
       <c r="F56" t="n">
-        <v>974.818</v>
+        <v>16120</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:18</t>
+          <t>2025-07-18 18:09:27</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3013,41 +3011,41 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>00937B</t>
+          <t>00934</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">群益ESG投等債20+     </t>
+          <t>中信成長高股息</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>145000</v>
+        <v>34859</v>
       </c>
       <c r="E57" t="n">
-        <v>0.082</v>
+        <v>0.023</v>
       </c>
       <c r="F57" t="n">
-        <v>11890</v>
+        <v>801.7569999999999</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:59</t>
+          <t>2025-07-18 18:10:01</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -3059,36 +3057,36 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>00948B</t>
+          <t>00937B</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">中信優息投資級債        </t>
+          <t xml:space="preserve">群益ESG投等債20+     </t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>160000</v>
+        <v>145000</v>
       </c>
       <c r="E58" t="n">
-        <v>0.042</v>
+        <v>0.082</v>
       </c>
       <c r="F58" t="n">
-        <v>6720</v>
+        <v>11890</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>2025-01-17</t>
+          <t>2024-12-20</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:58</t>
+          <t>2025-07-18 18:09:23</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3105,36 +3103,36 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2024-12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>00959B</t>
+          <t>00948B</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">大華投等美債15Y+      </t>
+          <t xml:space="preserve">中信優息投資級債        </t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>20000</v>
+        <v>160000</v>
       </c>
       <c r="E59" t="n">
         <v>0.052</v>
       </c>
       <c r="F59" t="n">
-        <v>1040</v>
+        <v>8320</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>2025-01-03</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:53</t>
+          <t>2025-07-18 18:09:39</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3151,36 +3149,36 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>00878</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>53166</v>
+        <v>16636</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5</v>
+        <v>1.07</v>
       </c>
       <c r="F60" t="n">
-        <v>26583</v>
+        <v>17800.52</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:20</t>
+          <t>2025-07-18 18:10:45</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3197,7 +3195,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3211,22 +3209,22 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>39650</v>
+        <v>37493</v>
       </c>
       <c r="E61" t="n">
         <v>0.026</v>
       </c>
       <c r="F61" t="n">
-        <v>1030.9</v>
+        <v>974.818</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:18</t>
+          <t>2025-07-18 18:10:47</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3243,7 +3241,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3267,12 +3265,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-01-22</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:59</t>
+          <t>2025-07-18 18:10:28</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3289,7 +3287,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3306,19 +3304,19 @@
         <v>160000</v>
       </c>
       <c r="E63" t="n">
-        <v>0.045</v>
+        <v>0.042</v>
       </c>
       <c r="F63" t="n">
-        <v>7200</v>
+        <v>6720</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
+          <t>2025-01-17</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:58</t>
+          <t>2025-07-18 18:10:27</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3335,7 +3333,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2025-01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -3349,22 +3347,22 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="E64" t="n">
-        <v>0.05</v>
+        <v>0.052</v>
       </c>
       <c r="F64" t="n">
-        <v>1250</v>
+        <v>1040</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2025-02-12</t>
+          <t>2025-01-03</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:53</t>
+          <t>2025-07-18 18:10:22</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3381,41 +3379,41 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>00687B</t>
+          <t>00878</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t xml:space="preserve">國泰20年美債         </t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5000</v>
+        <v>53166</v>
       </c>
       <c r="E65" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="F65" t="n">
-        <v>1750</v>
+        <v>26583</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:02</t>
+          <t>2025-07-18 18:10:49</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3427,36 +3425,36 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00934</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>中信成長高股息</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>17980</v>
+        <v>39650</v>
       </c>
       <c r="E66" t="n">
-        <v>1.4</v>
+        <v>0.026</v>
       </c>
       <c r="F66" t="n">
-        <v>25172</v>
+        <v>1030.9</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:22</t>
+          <t>2025-07-18 18:10:47</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3473,36 +3471,36 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>00751B</t>
+          <t>00937B</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t xml:space="preserve">元大AAA至A公司債      </t>
+          <t xml:space="preserve">群益ESG投等債20+     </t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>52000</v>
+        <v>145000</v>
       </c>
       <c r="E67" t="n">
-        <v>0.45</v>
+        <v>0.082</v>
       </c>
       <c r="F67" t="n">
-        <v>23400</v>
+        <v>11890</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>2025-03-21</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:03</t>
+          <t>2025-07-18 18:10:28</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3519,36 +3517,36 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>00857B</t>
+          <t>00948B</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t xml:space="preserve">永豐20年美公債        </t>
+          <t xml:space="preserve">中信優息投資級債        </t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>57000</v>
+        <v>160000</v>
       </c>
       <c r="E68" t="n">
-        <v>0.32</v>
+        <v>0.045</v>
       </c>
       <c r="F68" t="n">
-        <v>18240</v>
+        <v>7200</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-02-18</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:03</t>
+          <t>2025-07-18 18:10:27</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3565,41 +3563,41 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2025-02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>00934</t>
+          <t>00959B</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>中信成長高股息</t>
+          <t xml:space="preserve">大華投等美債15Y+      </t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>41786</v>
+        <v>25000</v>
       </c>
       <c r="E69" t="n">
-        <v>0.026</v>
+        <v>0.05</v>
       </c>
       <c r="F69" t="n">
-        <v>1086.436</v>
+        <v>1250</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:18</t>
+          <t>2025-07-18 18:10:22</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3616,22 +3614,22 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>00937B</t>
+          <t>00687B</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t xml:space="preserve">群益ESG投等債20+     </t>
+          <t xml:space="preserve">國泰20年美債         </t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>145000</v>
+        <v>5000</v>
       </c>
       <c r="E70" t="n">
-        <v>0.08</v>
+        <v>0.35</v>
       </c>
       <c r="F70" t="n">
-        <v>11600</v>
+        <v>1750</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3640,7 +3638,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:59</t>
+          <t>2025-07-18 18:10:31</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3662,36 +3660,36 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>00948B</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t xml:space="preserve">中信優息投資級債        </t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>160000</v>
+        <v>17980</v>
       </c>
       <c r="E71" t="n">
-        <v>0.048</v>
+        <v>1.4</v>
       </c>
       <c r="F71" t="n">
-        <v>7680</v>
+        <v>25172</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>2025-03-18</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:58</t>
+          <t>2025-07-18 18:10:51</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3708,31 +3706,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>00959B</t>
+          <t>00751B</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t xml:space="preserve">大華投等美債15Y+      </t>
+          <t xml:space="preserve">元大AAA至A公司債      </t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>25000</v>
+        <v>52000</v>
       </c>
       <c r="E72" t="n">
-        <v>0.05</v>
+        <v>0.45</v>
       </c>
       <c r="F72" t="n">
-        <v>1250</v>
+        <v>23400</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2025-03-21</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:53</t>
+          <t>2025-07-18 18:10:32</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3754,36 +3752,36 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>00857B</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>全台</t>
+          <t xml:space="preserve">永豐20年美公債        </t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>4000</v>
+        <v>57000</v>
       </c>
       <c r="E73" t="n">
-        <v>1.5</v>
+        <v>0.32</v>
       </c>
       <c r="F73" t="n">
-        <v>6000</v>
+        <v>18240</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2025-03-27</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:23</t>
+          <t>2025-07-18 18:10:32</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -3795,36 +3793,36 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>00934</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t>中信成長高股息</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>18274</v>
+        <v>41786</v>
       </c>
       <c r="E74" t="n">
-        <v>1.07</v>
+        <v>0.026</v>
       </c>
       <c r="F74" t="n">
-        <v>19553.18</v>
+        <v>1086.436</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2025-04-23</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:16</t>
+          <t>2025-07-18 18:10:47</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3841,41 +3839,41 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>00934</t>
+          <t>00937B</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>中信成長高股息</t>
+          <t xml:space="preserve">群益ESG投等債20+     </t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>44208</v>
+        <v>145000</v>
       </c>
       <c r="E75" t="n">
-        <v>0.026</v>
+        <v>0.08</v>
       </c>
       <c r="F75" t="n">
-        <v>1149.408</v>
+        <v>11600</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:18</t>
+          <t>2025-07-18 18:10:28</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -3887,36 +3885,36 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>00937B</t>
+          <t>00948B</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t xml:space="preserve">群益ESG投等債20+     </t>
+          <t xml:space="preserve">中信優息投資級債        </t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>171000</v>
+        <v>160000</v>
       </c>
       <c r="E76" t="n">
-        <v>0.08</v>
+        <v>0.048</v>
       </c>
       <c r="F76" t="n">
-        <v>13680</v>
+        <v>7680</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:59</t>
+          <t>2025-07-18 18:10:27</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3933,36 +3931,36 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>00948B</t>
+          <t>00959B</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t xml:space="preserve">中信優息投資級債        </t>
+          <t xml:space="preserve">大華投等美債15Y+      </t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>160000</v>
+        <v>25000</v>
       </c>
       <c r="E77" t="n">
-        <v>0.048</v>
+        <v>0.05</v>
       </c>
       <c r="F77" t="n">
-        <v>7680</v>
+        <v>1250</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:58</t>
+          <t>2025-07-18 18:10:22</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3979,41 +3977,41 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2025-03</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>00959B</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t xml:space="preserve">大華投等美債15Y+      </t>
+          <t>全台</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>25000</v>
+        <v>4000</v>
       </c>
       <c r="E78" t="n">
-        <v>0.043</v>
+        <v>1.5</v>
       </c>
       <c r="F78" t="n">
-        <v>1075</v>
+        <v>6000</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2025-04-02</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:53</t>
+          <t>2025-07-18 18:10:52</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -4030,31 +4028,31 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>4104</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>佳醫</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1050</v>
+        <v>18274</v>
       </c>
       <c r="E79" t="n">
-        <v>3.8</v>
+        <v>1.07</v>
       </c>
       <c r="F79" t="n">
-        <v>3990</v>
+        <v>19553.18</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-23</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:24</t>
+          <t>2025-07-18 18:10:45</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4071,36 +4069,36 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>00878</t>
+          <t>00934</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>國泰永續高股息</t>
+          <t>中信成長高股息</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>53166</v>
+        <v>44208</v>
       </c>
       <c r="E80" t="n">
-        <v>0.47</v>
+        <v>0.026</v>
       </c>
       <c r="F80" t="n">
-        <v>24988.02</v>
+        <v>1149.408</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:20</t>
+          <t>2025-07-18 18:10:47</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4117,41 +4115,41 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>00934</t>
+          <t>00937B</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>中信成長高股息</t>
+          <t xml:space="preserve">群益ESG投等債20+     </t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>46520</v>
+        <v>171000</v>
       </c>
       <c r="E81" t="n">
-        <v>0.026</v>
+        <v>0.08</v>
       </c>
       <c r="F81" t="n">
-        <v>1209.52</v>
+        <v>13680</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:18</t>
+          <t>2025-07-18 18:10:28</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -4163,36 +4161,36 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>00937B</t>
+          <t>00948B</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t xml:space="preserve">群益ESG投等債20+     </t>
+          <t xml:space="preserve">中信優息投資級債        </t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>171000</v>
+        <v>160000</v>
       </c>
       <c r="E82" t="n">
-        <v>0.077</v>
+        <v>0.048</v>
       </c>
       <c r="F82" t="n">
-        <v>13167</v>
+        <v>7680</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:59</t>
+          <t>2025-07-18 18:10:27</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4209,36 +4207,36 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>00948B</t>
+          <t>00959B</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t xml:space="preserve">中信優息投資級債        </t>
+          <t xml:space="preserve">大華投等美債15Y+      </t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>160000</v>
+        <v>25000</v>
       </c>
       <c r="E83" t="n">
-        <v>0.048</v>
+        <v>0.043</v>
       </c>
       <c r="F83" t="n">
-        <v>7680</v>
+        <v>1075</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2025-05-19</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:58</t>
+          <t>2025-07-18 18:10:22</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4255,41 +4253,41 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2025-04</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>00959B</t>
+          <t>4104</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t xml:space="preserve">大華投等美債15Y+      </t>
+          <t>佳醫</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>25000</v>
+        <v>1050</v>
       </c>
       <c r="E84" t="n">
-        <v>0.048</v>
+        <v>3.8</v>
       </c>
       <c r="F84" t="n">
-        <v>1200</v>
+        <v>3990</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>2025-05-05</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:53</t>
+          <t>2025-07-18 18:10:53</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -4301,41 +4299,41 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>00687B</t>
+          <t>00878</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t xml:space="preserve">國泰20年美債         </t>
+          <t>國泰永續高股息</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>5000</v>
+        <v>53166</v>
       </c>
       <c r="E85" t="n">
-        <v>0.31</v>
+        <v>0.47</v>
       </c>
       <c r="F85" t="n">
-        <v>1550</v>
+        <v>24988.02</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:02</t>
+          <t>2025-07-18 18:10:49</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -4347,36 +4345,36 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>00713</t>
+          <t>00934</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>元大台灣高息低波</t>
+          <t>中信成長高股息</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>24269</v>
+        <v>46520</v>
       </c>
       <c r="E86" t="n">
-        <v>1.1</v>
+        <v>0.026</v>
       </c>
       <c r="F86" t="n">
-        <v>26695.9</v>
+        <v>1209.52</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:22</t>
+          <t>2025-07-18 18:10:47</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4393,36 +4391,36 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>00751B</t>
+          <t>00937B</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t xml:space="preserve">元大AAA至A公司債      </t>
+          <t xml:space="preserve">群益ESG投等債20+     </t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>52000</v>
+        <v>171000</v>
       </c>
       <c r="E87" t="n">
-        <v>0.41</v>
+        <v>0.077</v>
       </c>
       <c r="F87" t="n">
-        <v>21320</v>
+        <v>13167</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:03</t>
+          <t>2025-07-18 18:10:28</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4439,36 +4437,36 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>00857B</t>
+          <t>00948B</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t xml:space="preserve">永豐20年美公債        </t>
+          <t xml:space="preserve">中信優息投資級債        </t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>57000</v>
+        <v>160000</v>
       </c>
       <c r="E88" t="n">
-        <v>0.28</v>
+        <v>0.048</v>
       </c>
       <c r="F88" t="n">
-        <v>15960</v>
+        <v>7680</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-05-19</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:03</t>
+          <t>2025-07-18 18:10:27</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4485,41 +4483,41 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>00934</t>
+          <t>00959B</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>中信成長高股息</t>
+          <t xml:space="preserve">大華投等美債15Y+      </t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>48737</v>
+        <v>25000</v>
       </c>
       <c r="E89" t="n">
-        <v>0.028</v>
+        <v>0.048</v>
       </c>
       <c r="F89" t="n">
-        <v>1364.636</v>
+        <v>1200</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-05-05</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:18</t>
+          <t>2025-07-18 18:10:22</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -4536,41 +4534,41 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>00937B</t>
+          <t>00687B</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>群益ESG投等債20+</t>
+          <t xml:space="preserve">國泰20年美債         </t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>2300</v>
+        <v>5000</v>
       </c>
       <c r="E90" t="n">
-        <v>0.077</v>
+        <v>0.31</v>
       </c>
       <c r="F90" t="n">
-        <v>177.1</v>
+        <v>1550</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>114/06/17</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2025-07-16 10:02:10</t>
+          <t>2025-07-18 18:10:31</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>櫃買中心</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>來源欄位: 息值</t>
+          <t>歷史回朔計算-實際配息日期</t>
         </is>
       </c>
     </row>
@@ -4582,36 +4580,36 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>00937B</t>
+          <t>00713</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t xml:space="preserve">群益ESG投等債20+     </t>
+          <t>元大台灣高息低波</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>171000</v>
+        <v>24269</v>
       </c>
       <c r="E91" t="n">
-        <v>0.077</v>
+        <v>1.1</v>
       </c>
       <c r="F91" t="n">
-        <v>13167</v>
+        <v>26695.9</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:59</t>
+          <t>2025-07-18 18:10:51</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -4628,31 +4626,31 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>00948B</t>
+          <t>00751B</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t xml:space="preserve">中信優息投資級債        </t>
+          <t xml:space="preserve">元大AAA至A公司債      </t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>160000</v>
+        <v>52000</v>
       </c>
       <c r="E92" t="n">
-        <v>0.046</v>
+        <v>0.41</v>
       </c>
       <c r="F92" t="n">
-        <v>7360</v>
+        <v>21320</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:58</t>
+          <t>2025-07-18 18:10:32</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4674,31 +4672,31 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>00959B</t>
+          <t>00857B</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t xml:space="preserve">大華投等美債15Y+      </t>
+          <t xml:space="preserve">永豐20年美公債        </t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>25000</v>
+        <v>57000</v>
       </c>
       <c r="E93" t="n">
-        <v>0.048</v>
+        <v>0.28</v>
       </c>
       <c r="F93" t="n">
-        <v>1200</v>
+        <v>15960</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>2025-06-04</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:53</t>
+          <t>2025-07-18 18:10:32</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4720,22 +4718,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>00934</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>群光</t>
+          <t>中信成長高股息</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1000</v>
+        <v>48737</v>
       </c>
       <c r="E94" t="n">
-        <v>10</v>
+        <v>0.028</v>
       </c>
       <c r="F94" t="n">
-        <v>10000</v>
+        <v>1364.636</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4744,7 +4742,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:27</t>
+          <t>2025-07-18 18:10:47</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4766,36 +4764,36 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2903</t>
+          <t>00937B</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>遠百</t>
+          <t xml:space="preserve">群益ESG投等債20+     </t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>2000</v>
+        <v>171000</v>
       </c>
       <c r="E95" t="n">
-        <v>1.35</v>
+        <v>0.077</v>
       </c>
       <c r="F95" t="n">
-        <v>2700</v>
+        <v>13167</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:29</t>
+          <t>2025-07-18 18:10:28</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -4812,36 +4810,36 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>00948B</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t xml:space="preserve">中信優息投資級債        </t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1000</v>
+        <v>160000</v>
       </c>
       <c r="E96" t="n">
-        <v>4.8</v>
+        <v>0.046</v>
       </c>
       <c r="F96" t="n">
-        <v>4800</v>
+        <v>7360</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:26</t>
+          <t>2025-07-18 18:10:27</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -4853,41 +4851,41 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>00959B</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>元大高股息</t>
+          <t xml:space="preserve">大華投等美債15Y+      </t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>21407</v>
+        <v>25000</v>
       </c>
       <c r="E97" t="n">
-        <v>0.866</v>
+        <v>0.048</v>
       </c>
       <c r="F97" t="n">
-        <v>18538.462</v>
+        <v>1200</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:16</t>
+          <t>2025-07-18 18:10:22</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>TPEx</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
@@ -4899,36 +4897,36 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>00934</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>中信成長高股息</t>
+          <t>正新</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>50903</v>
+        <v>11800</v>
       </c>
       <c r="E98" t="n">
-        <v>0.077</v>
+        <v>2.4</v>
       </c>
       <c r="F98" t="n">
-        <v>3919.531</v>
+        <v>28320</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:18</t>
+          <t>2025-07-18 18:10:55</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4945,41 +4943,41 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>00937B</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t xml:space="preserve">群益ESG投等債20+     </t>
+          <t>群光</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>171000</v>
+        <v>1000</v>
       </c>
       <c r="E99" t="n">
-        <v>0.07199999999999999</v>
+        <v>10</v>
       </c>
       <c r="F99" t="n">
-        <v>12312</v>
+        <v>10000</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:59</t>
+          <t>2025-07-18 18:10:56</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -4991,41 +4989,41 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>00948B</t>
+          <t>2903</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t xml:space="preserve">中信優息投資級債        </t>
+          <t>遠百</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>160000</v>
+        <v>2000</v>
       </c>
       <c r="E100" t="n">
-        <v>0.044</v>
+        <v>1.35</v>
       </c>
       <c r="F100" t="n">
-        <v>7040</v>
+        <v>2700</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:58</t>
+          <t>2025-07-18 18:10:58</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -5037,41 +5035,41 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-06</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>00959B</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t xml:space="preserve">大華投等美債15Y+      </t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>25000</v>
+        <v>1000</v>
       </c>
       <c r="E101" t="n">
-        <v>0.048</v>
+        <v>4.8</v>
       </c>
       <c r="F101" t="n">
-        <v>1200</v>
+        <v>4800</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2025-07-18 16:13:53</t>
+          <t>2025-07-18 18:10:55</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>TPEx</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -5088,31 +5086,31 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>6605</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>帝寶</t>
+          <t>元大高股息</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>2300</v>
+        <v>21407</v>
       </c>
       <c r="E102" t="n">
-        <v>9</v>
+        <v>0.866</v>
       </c>
       <c r="F102" t="n">
-        <v>20700</v>
+        <v>18538.462</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2025-07-18 16:14:37</t>
+          <t>2025-07-18 18:10:45</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5134,41 +5132,2927 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
+          <t>00934</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>中信成長高股息</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>50903</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="F103" t="n">
+        <v>3919.531</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2025-07-18 18:10:47</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>TSE</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>歷史回朔計算-實際配息日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>00937B</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">群益ESG投等債20+     </t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>171000</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="F104" t="n">
+        <v>12312</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2025-07-18 18:10:28</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>TPEx</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>歷史回朔計算-實際配息日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>00948B</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中信優息投資級債        </t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>160000</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="F105" t="n">
+        <v>7040</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2025-07-18 18:10:27</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>TPEx</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>歷史回朔計算-實際配息日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>00959B</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大華投等美債15Y+      </t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1200</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2025-07-03</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2025-07-18 18:10:22</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>TPEx</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>歷史回朔計算-實際配息日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>6605</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>帝寶</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>2300</v>
+      </c>
+      <c r="E107" t="n">
+        <v>9</v>
+      </c>
+      <c r="F107" t="n">
+        <v>20700</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2025-07-18 18:11:06</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>TSE</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>歷史回朔計算-實際配息日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
           <t>8299</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t xml:space="preserve">群聯              </t>
         </is>
       </c>
-      <c r="D103" t="n">
+      <c r="D108" t="n">
         <v>10</v>
       </c>
-      <c r="E103" t="n">
+      <c r="E108" t="n">
         <v>11.958999</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F108" t="n">
         <v>119.58999</v>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>2025-07-01</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>2025-07-18 16:13:54</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2025-07-18 18:10:22</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
         <is>
           <t>TPEx</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>歷史回朔計算-實際配息日期</t>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>歷史回朔計算-實際配息日期</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>年份</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>總配息金額</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>配息次數</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>平均配息金額</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>股票檔數</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>累計配息金額</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>年度成長率(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>226282.56</v>
+      </c>
+      <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32326.08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>226282.56</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>695913.35</v>
+      </c>
+      <c r="C3" t="n">
+        <v>51</v>
+      </c>
+      <c r="D3" t="n">
+        <v>13645.36</v>
+      </c>
+      <c r="E3" t="n">
+        <v>16</v>
+      </c>
+      <c r="F3" t="n">
+        <v>922195.9099999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>207.54</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>476196.92</v>
+      </c>
+      <c r="C4" t="n">
+        <v>49</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9718.299999999999</v>
+      </c>
+      <c r="E4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1398392.83</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-31.57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>年月</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>總配息金額</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>配息次數</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>平均配息金額</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>股票檔數</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>年份</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>月份</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>累計配息金額</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>月度成長率(%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>16520</v>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>16520</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>16520</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>45060.11</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>22530.05</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>61580.11</v>
+      </c>
+      <c r="I3" t="n">
+        <v>172.76</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>164702.45</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>41175.61</v>
+      </c>
+      <c r="E4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>226282.56</v>
+      </c>
+      <c r="I4" t="n">
+        <v>265.52</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>17600</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>17600</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>243882.56</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-89.31</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>42920</v>
+      </c>
+      <c r="C6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" t="n">
+        <v>10730</v>
+      </c>
+      <c r="E6" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>286802.56</v>
+      </c>
+      <c r="I6" t="n">
+        <v>143.86</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>22687</v>
+      </c>
+      <c r="C7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" t="n">
+        <v>11343.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>309489.56</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-47.14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>35130</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>17565</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>344619.56</v>
+      </c>
+      <c r="I8" t="n">
+        <v>54.85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>75196.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>12532.75</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>419816.06</v>
+      </c>
+      <c r="I9" t="n">
+        <v>114.05</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>144260.23</v>
+      </c>
+      <c r="C10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" t="n">
+        <v>24043.37</v>
+      </c>
+      <c r="E10" t="n">
+        <v>6</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>564076.29</v>
+      </c>
+      <c r="I10" t="n">
+        <v>91.84</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>104505.24</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>14929.32</v>
+      </c>
+      <c r="E11" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>668581.53</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-27.56</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>76749.22</v>
+      </c>
+      <c r="C12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9593.65</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>745330.75</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-26.56</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>40967.01</v>
+      </c>
+      <c r="C13" t="n">
+        <v>4</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10241.75</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>786297.76</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-46.62</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>51519.39</v>
+      </c>
+      <c r="C14" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" t="n">
+        <v>12879.85</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>837817.15</v>
+      </c>
+      <c r="I14" t="n">
+        <v>25.76</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>84378.75999999999</v>
+      </c>
+      <c r="C15" t="n">
+        <v>7</v>
+      </c>
+      <c r="D15" t="n">
+        <v>12054.11</v>
+      </c>
+      <c r="E15" t="n">
+        <v>7</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>922195.91</v>
+      </c>
+      <c r="I15" t="n">
+        <v>63.78</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>38425.34</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="n">
+        <v>7685.07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>960621.25</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-54.46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>47953.9</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9590.780000000001</v>
+      </c>
+      <c r="E17" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>1008575.15</v>
+      </c>
+      <c r="I17" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>96178.44</v>
+      </c>
+      <c r="C18" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10686.49</v>
+      </c>
+      <c r="E18" t="n">
+        <v>9</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>1104753.59</v>
+      </c>
+      <c r="I18" t="n">
+        <v>100.56</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>47127.59</v>
+      </c>
+      <c r="C19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7854.6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>1151881.18</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-51</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>48244.54</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D20" t="n">
+        <v>9648.91</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>1200125.72</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.37</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>134437.54</v>
+      </c>
+      <c r="C21" t="n">
+        <v>12</v>
+      </c>
+      <c r="D21" t="n">
+        <v>11203.13</v>
+      </c>
+      <c r="E21" t="n">
+        <v>12</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>1334563.26</v>
+      </c>
+      <c r="I21" t="n">
+        <v>178.66</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>63829.58</v>
+      </c>
+      <c r="C22" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" t="n">
+        <v>9118.51</v>
+      </c>
+      <c r="E22" t="n">
+        <v>7</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>1398392.84</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-52.52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>股票代碼</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>股票名稱</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>總配息金額</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>配息次數</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>平均配息金額</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>最高配息金額</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>最低配息金額</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>平均每股配息</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>最高每股配息</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>最低每股配息</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>平均持有股數</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>首次配息年月</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>最後配息年月</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>配息期間(月)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>年化配息次數</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>00937B</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">群益ESG投等債20+     </t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>208056</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2" t="n">
+        <v>12238.59</v>
+      </c>
+      <c r="F2" t="n">
+        <v>13680</v>
+      </c>
+      <c r="G2" t="n">
+        <v>11600</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K2" t="n">
+        <v>151117.65</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>16</v>
+      </c>
+      <c r="O2" t="n">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>5871</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>中租-KY</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>154498.68</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>51499.56</v>
+      </c>
+      <c r="F3" t="n">
+        <v>94535.28999999999</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3022.22</v>
+      </c>
+      <c r="H3" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K3" t="n">
+        <v>8433.33</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>13</v>
+      </c>
+      <c r="O3" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>00878</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>國泰永續高股息</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>145820.82</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="n">
+        <v>24303.47</v>
+      </c>
+      <c r="F4" t="n">
+        <v>27603.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>17600</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>48828</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>00751B</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">元大AAA至A公司債      </t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>139880</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>23313.33</v>
+      </c>
+      <c r="F5" t="n">
+        <v>24440</v>
+      </c>
+      <c r="G5" t="n">
+        <v>21320</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="K5" t="n">
+        <v>52000</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>15</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>00713</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>元大台灣高息低波</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>111554.9</v>
+      </c>
+      <c r="D6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E6" t="n">
+        <v>18592.48</v>
+      </c>
+      <c r="F6" t="n">
+        <v>26695.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6160</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K6" t="n">
+        <v>14325.67</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>15</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0056</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>元大高股息</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>97878.56</v>
+      </c>
+      <c r="D7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16313.09</v>
+      </c>
+      <c r="F7" t="n">
+        <v>19553.18</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10507</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="K7" t="n">
+        <v>16506.17</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>15</v>
+      </c>
+      <c r="O7" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>00948B</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">中信優息投資級債        </t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>93760</v>
+      </c>
+      <c r="D8" t="n">
+        <v>12</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7813.33</v>
+      </c>
+      <c r="F8" t="n">
+        <v>8800</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6720</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K8" t="n">
+        <v>160000</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>11</v>
+      </c>
+      <c r="O8" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2105</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>正新</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>68440</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>22813.33</v>
+      </c>
+      <c r="F9" t="n">
+        <v>28320</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16520</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>11800</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>24</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>5871</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>中租-KY</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>56941.17</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>56941.17</v>
+      </c>
+      <c r="F10" t="n">
+        <v>56941.17</v>
+      </c>
+      <c r="G10" t="n">
+        <v>56941.17</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="I10" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="J10" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5500</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>00857B</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">永豐20年美公債        </t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>55840</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>11168</v>
+      </c>
+      <c r="F11" t="n">
+        <v>18240</v>
+      </c>
+      <c r="G11" t="n">
+        <v>420</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K11" t="n">
+        <v>37000</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>12</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>51123.06</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>25561.53</v>
+      </c>
+      <c r="F12" t="n">
+        <v>25713</v>
+      </c>
+      <c r="G12" t="n">
+        <v>25410.06</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="K12" t="n">
+        <v>15602</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2887</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>45640.15</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" t="n">
+        <v>22820.08</v>
+      </c>
+      <c r="F13" t="n">
+        <v>23110.1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>22530.05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="K13" t="n">
+        <v>17777</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>13</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2892</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>第一金</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>25410.06</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>25410.06</v>
+      </c>
+      <c r="F14" t="n">
+        <v>25410.06</v>
+      </c>
+      <c r="G14" t="n">
+        <v>25410.06</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="K14" t="n">
+        <v>15602</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>00934</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>中信成長高股息</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>24823.95</v>
+      </c>
+      <c r="D15" t="n">
+        <v>13</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1909.53</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3919.53</v>
+      </c>
+      <c r="G15" t="n">
+        <v>801.76</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="K15" t="n">
+        <v>33895</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>12</v>
+      </c>
+      <c r="O15" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2887</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>台新金</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>22530.05</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>22530.05</v>
+      </c>
+      <c r="F16" t="n">
+        <v>22530.05</v>
+      </c>
+      <c r="G16" t="n">
+        <v>22530.05</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="K16" t="n">
+        <v>17777</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6605</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>帝寶</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>20700</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>20700</v>
+      </c>
+      <c r="F17" t="n">
+        <v>20700</v>
+      </c>
+      <c r="G17" t="n">
+        <v>20700</v>
+      </c>
+      <c r="H17" t="n">
+        <v>9</v>
+      </c>
+      <c r="I17" t="n">
+        <v>9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>9</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2300</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2812</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>台中銀</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>15570.84</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>15570.84</v>
+      </c>
+      <c r="F18" t="n">
+        <v>15570.84</v>
+      </c>
+      <c r="G18" t="n">
+        <v>15570.84</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="K18" t="n">
+        <v>11000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3038</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>全台</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>12400</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>6200</v>
+      </c>
+      <c r="F19" t="n">
+        <v>6400</v>
+      </c>
+      <c r="G19" t="n">
+        <v>6000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>8</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00687B</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">國泰20年美債         </t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>10700</v>
+      </c>
+      <c r="D20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1783.33</v>
+      </c>
+      <c r="F20" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1550</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>15</v>
+      </c>
+      <c r="O20" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2385</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>群光</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H21" t="n">
+        <v>10</v>
+      </c>
+      <c r="I21" t="n">
+        <v>10</v>
+      </c>
+      <c r="J21" t="n">
+        <v>10</v>
+      </c>
+      <c r="K21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00959B</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">大華投等美債15Y+      </t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>8215</v>
+      </c>
+      <c r="D22" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1173.57</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1250</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1040</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="K22" t="n">
+        <v>24285.71</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="O22" t="n">
+        <v>14.2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>9942</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>茂順</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F23" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>7</v>
+      </c>
+      <c r="I23" t="n">
+        <v>7</v>
+      </c>
+      <c r="J23" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>4800</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4800</v>
+      </c>
+      <c r="G24" t="n">
+        <v>4800</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4104</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>佳醫</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>3990</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3990</v>
+      </c>
+      <c r="F25" t="n">
+        <v>3990</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3990</v>
+      </c>
+      <c r="H25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1050</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2903</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>遠百</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2700</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2700</v>
+      </c>
+      <c r="F26" t="n">
+        <v>2700</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2700</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2000</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>8299</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">群聯              </t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>119.59</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>119.59</v>
+      </c>
+      <c r="F27" t="n">
+        <v>119.59</v>
+      </c>
+      <c r="G27" t="n">
+        <v>119.59</v>
+      </c>
+      <c r="H27" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="I27" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="J27" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="K27" t="n">
+        <v>10</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>統計項目</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>數值</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>總配息收益</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1,398,392.83 元</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>所有配息記錄的總和</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>配息記錄總數</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>107 筆</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>所有配息記錄的數量</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>投資股票檔數</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26 檔</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>有配息記錄的股票數量</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>配息期間</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2023-06 ~ 2025-07</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>從最早到最晚的配息記錄</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>平均每筆配息</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>13069.09 元</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>每筆配息記錄的平均金額</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>平均每檔股票配息</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>53784.34 元</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>每檔股票的平均總配息</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>最高單筆配息</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>94535.29 元</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5871 (2024-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>最低單筆配息</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>119.59 元</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>8299 (2025-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>平均配息頻率</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>4.1 次/檔</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>每檔股票的平均配息次數</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>最高配息頻率</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>17 次</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>單一股票的最多配息次數</t>
         </is>
       </c>
     </row>

--- a/mystkdatav2/dividend_database.xlsx
+++ b/mystkdatav2/dividend_database.xlsx
@@ -3178,7 +3178,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:45</t>
+          <t>2025-07-21 06:30:41</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:47</t>
+          <t>2025-07-21 06:30:43</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:28</t>
+          <t>2025-07-21 06:30:25</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:27</t>
+          <t>2025-07-21 06:30:24</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:22</t>
+          <t>2025-07-21 06:30:20</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:49</t>
+          <t>2025-07-21 06:30:45</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:47</t>
+          <t>2025-07-21 06:30:43</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:28</t>
+          <t>2025-07-21 06:30:25</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:27</t>
+          <t>2025-07-21 06:30:24</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:22</t>
+          <t>2025-07-21 06:30:20</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:31</t>
+          <t>2025-07-21 06:30:28</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:51</t>
+          <t>2025-07-21 06:30:47</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:32</t>
+          <t>2025-07-21 06:30:29</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:32</t>
+          <t>2025-07-21 06:30:29</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:47</t>
+          <t>2025-07-21 06:30:43</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:28</t>
+          <t>2025-07-21 06:30:25</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:27</t>
+          <t>2025-07-21 06:30:24</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:22</t>
+          <t>2025-07-21 06:30:20</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:52</t>
+          <t>2025-07-21 06:30:47</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:45</t>
+          <t>2025-07-21 06:30:41</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:47</t>
+          <t>2025-07-21 06:30:43</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:28</t>
+          <t>2025-07-21 06:30:25</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:27</t>
+          <t>2025-07-21 06:30:25</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:22</t>
+          <t>2025-07-21 06:30:20</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:53</t>
+          <t>2025-07-21 06:30:49</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:49</t>
+          <t>2025-07-21 06:30:45</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:47</t>
+          <t>2025-07-21 06:30:43</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:28</t>
+          <t>2025-07-21 06:30:25</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:27</t>
+          <t>2025-07-21 06:30:25</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:22</t>
+          <t>2025-07-21 06:30:20</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:31</t>
+          <t>2025-07-21 06:30:28</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:51</t>
+          <t>2025-07-21 06:30:47</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:32</t>
+          <t>2025-07-21 06:30:29</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:32</t>
+          <t>2025-07-21 06:30:29</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:47</t>
+          <t>2025-07-21 06:30:43</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:28</t>
+          <t>2025-07-21 06:30:25</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:27</t>
+          <t>2025-07-21 06:30:25</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:22</t>
+          <t>2025-07-21 06:30:20</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:55</t>
+          <t>2025-07-21 06:30:50</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:56</t>
+          <t>2025-07-21 06:30:51</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:58</t>
+          <t>2025-07-21 06:30:53</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:55</t>
+          <t>2025-07-21 06:30:50</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:45</t>
+          <t>2025-07-21 06:30:42</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:47</t>
+          <t>2025-07-21 06:30:43</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:28</t>
+          <t>2025-07-21 06:30:25</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:27</t>
+          <t>2025-07-21 06:30:25</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:22</t>
+          <t>2025-07-21 06:30:20</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2025-07-18 18:11:06</t>
+          <t>2025-07-21 06:31:01</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2025-07-18 18:10:22</t>
+          <t>2025-07-21 06:30:20</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">

--- a/mystkdatav2/dividend_database.xlsx
+++ b/mystkdatav2/dividend_database.xlsx
@@ -3178,7 +3178,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:41</t>
+          <t>2025-07-23 06:30:33</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:43</t>
+          <t>2025-07-23 06:30:35</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:25</t>
+          <t>2025-07-23 06:30:17</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:24</t>
+          <t>2025-07-23 06:30:16</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:20</t>
+          <t>2025-07-23 06:30:11</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:45</t>
+          <t>2025-07-23 06:30:37</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:43</t>
+          <t>2025-07-23 06:30:35</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:25</t>
+          <t>2025-07-23 06:30:17</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:24</t>
+          <t>2025-07-23 06:30:16</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:20</t>
+          <t>2025-07-23 06:30:11</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:28</t>
+          <t>2025-07-23 06:30:20</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:47</t>
+          <t>2025-07-23 06:30:39</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:29</t>
+          <t>2025-07-23 06:30:21</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:29</t>
+          <t>2025-07-23 06:30:20</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:43</t>
+          <t>2025-07-23 06:30:35</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:25</t>
+          <t>2025-07-23 06:30:17</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:24</t>
+          <t>2025-07-23 06:30:16</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:20</t>
+          <t>2025-07-23 06:30:11</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:47</t>
+          <t>2025-07-23 06:30:39</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:41</t>
+          <t>2025-07-23 06:30:33</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:43</t>
+          <t>2025-07-23 06:30:35</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:25</t>
+          <t>2025-07-23 06:30:17</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:25</t>
+          <t>2025-07-23 06:30:16</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:20</t>
+          <t>2025-07-23 06:30:11</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:49</t>
+          <t>2025-07-23 06:30:41</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:45</t>
+          <t>2025-07-23 06:30:37</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:43</t>
+          <t>2025-07-23 06:30:35</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:25</t>
+          <t>2025-07-23 06:30:17</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:25</t>
+          <t>2025-07-23 06:30:16</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:20</t>
+          <t>2025-07-23 06:30:11</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:28</t>
+          <t>2025-07-23 06:30:20</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:47</t>
+          <t>2025-07-23 06:30:39</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:29</t>
+          <t>2025-07-23 06:30:21</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:29</t>
+          <t>2025-07-23 06:30:21</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:43</t>
+          <t>2025-07-23 06:30:35</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:25</t>
+          <t>2025-07-23 06:30:17</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:25</t>
+          <t>2025-07-23 06:30:16</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:20</t>
+          <t>2025-07-23 06:30:11</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:50</t>
+          <t>2025-07-23 06:30:42</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:51</t>
+          <t>2025-07-23 06:30:43</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:53</t>
+          <t>2025-07-23 06:30:45</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:50</t>
+          <t>2025-07-23 06:30:42</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:42</t>
+          <t>2025-07-23 06:30:33</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:43</t>
+          <t>2025-07-23 06:30:35</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:25</t>
+          <t>2025-07-23 06:30:17</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:25</t>
+          <t>2025-07-23 06:30:16</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:20</t>
+          <t>2025-07-23 06:30:11</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2025-07-21 06:31:01</t>
+          <t>2025-07-23 06:30:53</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2025-07-21 06:30:20</t>
+          <t>2025-07-23 06:30:11</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">

--- a/mystkdatav2/dividend_database.xlsx
+++ b/mystkdatav2/dividend_database.xlsx
@@ -3178,7 +3178,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:33</t>
+          <t>2025-07-24 06:30:39</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:35</t>
+          <t>2025-07-24 06:30:40</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:17</t>
+          <t>2025-07-24 06:30:22</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:16</t>
+          <t>2025-07-24 06:30:21</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:11</t>
+          <t>2025-07-24 06:30:17</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:37</t>
+          <t>2025-07-24 06:30:42</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:35</t>
+          <t>2025-07-24 06:30:40</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3500,7 +3500,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:17</t>
+          <t>2025-07-24 06:30:22</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:16</t>
+          <t>2025-07-24 06:30:21</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3592,7 +3592,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:11</t>
+          <t>2025-07-24 06:30:17</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:20</t>
+          <t>2025-07-24 06:30:25</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:39</t>
+          <t>2025-07-24 06:30:44</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3730,7 +3730,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:21</t>
+          <t>2025-07-24 06:30:26</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:20</t>
+          <t>2025-07-24 06:30:26</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:35</t>
+          <t>2025-07-24 06:30:40</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3868,7 +3868,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:17</t>
+          <t>2025-07-24 06:30:22</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:16</t>
+          <t>2025-07-24 06:30:21</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:11</t>
+          <t>2025-07-24 06:30:17</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:39</t>
+          <t>2025-07-24 06:30:45</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:33</t>
+          <t>2025-07-24 06:30:39</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:35</t>
+          <t>2025-07-24 06:30:40</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:17</t>
+          <t>2025-07-24 06:30:22</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:16</t>
+          <t>2025-07-24 06:30:21</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:11</t>
+          <t>2025-07-24 06:30:17</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:41</t>
+          <t>2025-07-24 06:30:46</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:37</t>
+          <t>2025-07-24 06:30:42</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:35</t>
+          <t>2025-07-24 06:30:40</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:17</t>
+          <t>2025-07-24 06:30:22</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:16</t>
+          <t>2025-07-24 06:30:21</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:11</t>
+          <t>2025-07-24 06:30:17</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:20</t>
+          <t>2025-07-24 06:30:25</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:39</t>
+          <t>2025-07-24 06:30:44</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4650,7 +4650,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:21</t>
+          <t>2025-07-24 06:30:26</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:21</t>
+          <t>2025-07-24 06:30:26</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:35</t>
+          <t>2025-07-24 06:30:40</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:17</t>
+          <t>2025-07-24 06:30:22</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:16</t>
+          <t>2025-07-24 06:30:21</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:11</t>
+          <t>2025-07-24 06:30:17</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:42</t>
+          <t>2025-07-24 06:30:48</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:43</t>
+          <t>2025-07-24 06:30:49</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:45</t>
+          <t>2025-07-24 06:30:51</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:42</t>
+          <t>2025-07-24 06:30:48</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:33</t>
+          <t>2025-07-24 06:30:39</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:35</t>
+          <t>2025-07-24 06:30:40</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:17</t>
+          <t>2025-07-24 06:30:22</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:16</t>
+          <t>2025-07-24 06:30:21</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:11</t>
+          <t>2025-07-24 06:30:17</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:53</t>
+          <t>2025-07-24 06:30:58</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2025-07-23 06:30:11</t>
+          <t>2025-07-24 06:30:17</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
